--- a/data/Control_GDE_obras_a_licitar.xlsx
+++ b/data/Control_GDE_obras_a_licitar.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jmlopez\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jmlopez\Desktop\epas-dashboard-v2\epas-dashboard-v2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0484BC5D-078E-481C-978D-6D2CE94015C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B60FCD4-623C-47A2-96BF-353AC9D5EFB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>Localidad</t>
   </si>
@@ -86,6 +86,15 @@
   </si>
   <si>
     <t>Fecha Apertura</t>
+  </si>
+  <si>
+    <t>Taquimilan</t>
+  </si>
+  <si>
+    <t>OBRA “SISTEMA CLOACAL – 1º ETAPA”</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> EX-2026-02351076- -NEU-SECGRAL#EPAS</t>
   </si>
 </sst>
 </file>
@@ -154,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -202,11 +211,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -488,10 +512,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:F29"/>
+  <dimension ref="A2:F30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="33.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34.19921875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="46.53125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.1328125" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.1328125" style="1" customWidth="1"/>
@@ -519,81 +543,93 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="16" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A3" s="17" t="s">
+    <row r="3" spans="1:6" s="21" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="19">
+        <v>46266</v>
+      </c>
+      <c r="E3" s="20">
+        <v>3086884525.8099999</v>
+      </c>
+      <c r="F3" s="20">
+        <v>3052854773.6799998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" s="16" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A4" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B4" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C4" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="18">
+      <c r="D4" s="17">
         <v>46287</v>
       </c>
-      <c r="E3" s="15">
+      <c r="E4" s="15">
         <v>88500000</v>
       </c>
-      <c r="F3" s="15"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A4" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="10">
-        <v>598328125.25999999</v>
-      </c>
-      <c r="F4" s="10"/>
+      <c r="F4" s="15"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="5"/>
+      <c r="E5" s="10">
+        <v>598328125.25999999</v>
+      </c>
+      <c r="F5" s="10"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A6" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C6" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D6" s="5">
         <v>46287</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E6" s="10">
         <v>158000000</v>
       </c>
-      <c r="F5" s="10"/>
-    </row>
-    <row r="6" spans="1:6" s="16" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A6" s="12" t="s">
+      <c r="F6" s="10"/>
+    </row>
+    <row r="7" spans="1:6" s="16" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A7" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B7" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C7" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="18"/>
-      <c r="E6" s="15">
+      <c r="D7" s="17"/>
+      <c r="E7" s="15">
         <v>1440466165.5699999</v>
       </c>
-      <c r="F6" s="15"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
+      <c r="F7" s="15"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="6"/>
@@ -619,21 +655,21 @@
       <c r="E10" s="10"/>
       <c r="F10" s="10"/>
     </row>
-    <row r="11" spans="1:6" s="16" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="12"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="5"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+    </row>
+    <row r="12" spans="1:6" s="16" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="12"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" s="6"/>
@@ -771,6 +807,14 @@
       <c r="E29" s="10"/>
       <c r="F29" s="10"/>
     </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data/Control_GDE_obras_a_licitar.xlsx
+++ b/data/Control_GDE_obras_a_licitar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jmlopez\Desktop\epas-dashboard-v2\epas-dashboard-v2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F69AA8F-E0E6-4DE3-88B8-AE14E2A72F8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E373C73E-BFBC-48A0-B1C8-F7144737713C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="38">
   <si>
     <t>Localidad</t>
   </si>
@@ -131,6 +131,24 @@
   </si>
   <si>
     <t>El Alamito</t>
+  </si>
+  <si>
+    <t>OBRA: "SISTEMA DE AGUA POTABLE - CISTERNA LOS VOLCANES"</t>
+  </si>
+  <si>
+    <t>EX-2026-03114394- -NEU-SECGRAL#EPAS</t>
+  </si>
+  <si>
+    <t>EX-2026-03114363- -NEU-SECGRAL#EPAS</t>
+  </si>
+  <si>
+    <t>OBRA: "SISTEMA DE AGUA POTABLE - CISTERNA ARROYO EL COLORADO"</t>
+  </si>
+  <si>
+    <t>EX-2026-03114304- -NEU-SECGRAL#EPAS</t>
+  </si>
+  <si>
+    <t>OBRA: "SISTEMA DE AGUA POTABLE - CISTERNA LOMAS DEL CORRENTOSO"</t>
   </si>
 </sst>
 </file>
@@ -540,7 +558,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="34.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="48.53125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="60.9296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="15.1328125" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.1328125" style="1" customWidth="1"/>
     <col min="5" max="5" width="16.265625" style="11" bestFit="1" customWidth="1"/>
@@ -597,8 +615,8 @@
       <c r="C4" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="17">
-        <v>46287</v>
+      <c r="D4" s="17" t="s">
+        <v>25</v>
       </c>
       <c r="E4" s="15">
         <v>88500000</v>
@@ -637,7 +655,9 @@
       <c r="E6" s="10">
         <v>158000000</v>
       </c>
-      <c r="F6" s="10"/>
+      <c r="F6" s="10">
+        <v>124964522.31</v>
+      </c>
     </row>
     <row r="7" spans="1:6" s="16" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A7" s="12" t="s">
@@ -730,27 +750,57 @@
       <c r="F11" s="10"/>
     </row>
     <row r="12" spans="1:6" s="16" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="15"/>
+      <c r="A12" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="15">
+        <v>628372676.10000002</v>
+      </c>
       <c r="F12" s="15"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="10"/>
+      <c r="A13" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="10">
+        <v>645356365.63999999</v>
+      </c>
       <c r="F13" s="10"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="10"/>
+      <c r="A14" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="10">
+        <v>639910967.13</v>
+      </c>
       <c r="F14" s="10"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.45">
@@ -882,7 +932,7 @@
       <c r="F30" s="10"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>